--- a/data/iNat_data_comparison.xlsx
+++ b/data/iNat_data_comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susanacunha/Documents/PhD/iNat_analysis_clean/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECB1DFB-9925-5442-AEA6-788F9C941FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EEDB51-CC2C-D942-9F15-88B2159732BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8160" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{4941AD39-BC8E-484C-BCA5-3AF58B923FA9}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" activeTab="1" xr2:uid="{4941AD39-BC8E-484C-BCA5-3AF58B923FA9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>Vertebrates</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>RG/verifiable_global</t>
+  </si>
+  <si>
+    <t>global_total</t>
   </si>
 </sst>
 </file>
@@ -188,7 +191,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -196,6 +199,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -532,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7502C8B3-EC9E-9448-BAE6-0C581C8619DE}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
@@ -542,9 +546,12 @@
     <col min="5" max="5" width="22.83203125" customWidth="1"/>
     <col min="6" max="7" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
@@ -584,8 +591,14 @@
       <c r="M1" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -620,7 +633,7 @@
         <v>0.82367721989807074</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -655,7 +668,7 @@
         <v>0.6620445365607357</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -691,7 +704,7 @@
       </c>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -725,18 +738,25 @@
         <f t="shared" si="1"/>
         <v>0.43446169972949494</v>
       </c>
-      <c r="K5">
-        <v>21142713</v>
-      </c>
-      <c r="L5">
-        <v>6109070</v>
-      </c>
-      <c r="M5">
+      <c r="K5" s="7">
+        <v>11966484</v>
+      </c>
+      <c r="L5" s="7">
+        <v>3790525</v>
+      </c>
+      <c r="M5" s="7">
         <f>L5/K5</f>
-        <v>0.2889444698984468</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+        <v>0.31676179903804658</v>
+      </c>
+      <c r="N5" s="7">
+        <v>12247435</v>
+      </c>
+      <c r="O5">
+        <f>L5/N5</f>
+        <v>0.30949541679543513</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -746,7 +766,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="F7" s="6"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
